--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="426">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,6 +274,9 @@
     <t>ControlAct[moodCode=INT]</t>
   </si>
   <si>
+    <t>workflow.order</t>
+  </si>
+  <si>
     <t>Task.id</t>
   </si>
   <si>
@@ -357,7 +360,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,6 +418,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -455,7 +462,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -594,7 +601,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/task-status|4.3.0</t>
   </si>
   <si>
     <t>Request.status, Event.status</t>
@@ -665,7 +672,7 @@
     <t>Distinguishes whether the task is a proposal, plan or full order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/task-intent|4.3.0</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -692,10 +699,10 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>The task's priority.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>The priority of a task (may affect service level applied to the task).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -1121,6 +1128,10 @@
   </si>
   <si>
     <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
@@ -1917,7 +1928,7 @@
         <v>84</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>77</v>
@@ -1925,10 +1936,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1939,7 +1950,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1948,19 +1959,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2010,13 +2021,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2039,10 +2050,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2053,7 +2064,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2062,16 +2073,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2122,19 +2133,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2151,10 +2162,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2165,28 +2176,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2236,19 +2247,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2265,10 +2276,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2279,7 +2290,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2291,16 +2302,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2326,13 +2337,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2350,19 +2361,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2379,21 +2390,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2405,16 +2416,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2464,25 +2475,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2493,14 +2504,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2519,16 +2530,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2578,7 +2589,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2590,13 +2601,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2607,14 +2618,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2633,16 +2644,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2692,7 +2703,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2704,13 +2715,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2721,14 +2732,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2741,25 +2752,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2808,7 +2819,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2820,13 +2831,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2837,10 +2848,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2863,13 +2874,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2920,7 +2931,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2932,16 +2943,16 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>77</v>
@@ -2949,10 +2960,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2963,7 +2974,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2972,20 +2983,20 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3034,25 +3045,25 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3063,10 +3074,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3077,7 +3088,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3086,20 +3097,20 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3148,25 +3159,25 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3177,10 +3188,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3200,16 +3211,16 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3260,7 +3271,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3272,13 +3283,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3289,10 +3300,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3303,7 +3314,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3312,20 +3323,20 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3374,25 +3385,25 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3403,10 +3414,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3426,22 +3437,22 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3490,7 +3501,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3502,13 +3513,13 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3519,10 +3530,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3530,32 +3541,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3580,52 +3591,52 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>181</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3633,10 +3644,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3647,7 +3658,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3656,19 +3667,19 @@
         <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3694,10 +3705,10 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>77</v>
@@ -3718,25 +3729,25 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3747,10 +3758,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3761,7 +3772,7 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
@@ -3770,20 +3781,20 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3808,10 +3819,10 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>77</v>
@@ -3832,25 +3843,25 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3861,10 +3872,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3872,10 +3883,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3884,19 +3895,19 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3922,13 +3933,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3946,28 +3957,28 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3975,10 +3986,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3989,7 +4000,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4001,23 +4012,23 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>77</v>
@@ -4038,13 +4049,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -4062,28 +4073,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4091,10 +4102,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4105,7 +4116,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4114,19 +4125,19 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4152,13 +4163,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4176,28 +4187,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4205,10 +4216,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4219,7 +4230,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4228,16 +4239,16 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4288,25 +4299,25 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4317,10 +4328,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4331,7 +4342,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4340,22 +4351,22 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4404,28 +4415,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4433,21 +4444,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4456,20 +4467,20 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4518,28 +4529,28 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4547,10 +4558,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4561,7 +4572,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4570,20 +4581,20 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4632,28 +4643,28 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4661,10 +4672,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4672,10 +4683,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4684,16 +4695,16 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4744,28 +4755,28 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4773,21 +4784,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4799,17 +4810,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4858,28 +4869,28 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4887,21 +4898,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4910,20 +4921,20 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4972,25 +4983,25 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5001,10 +5012,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5015,7 +5026,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5024,20 +5035,20 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5086,28 +5097,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5115,10 +5126,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5141,17 +5152,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5176,13 +5187,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5200,7 +5211,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5212,16 +5223,16 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5229,21 +5240,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
@@ -5252,22 +5263,22 @@
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5316,28 +5327,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5345,10 +5356,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5359,7 +5370,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>77</v>
@@ -5368,20 +5379,20 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5430,28 +5441,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5459,10 +5470,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5473,7 +5484,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5485,16 +5496,16 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5520,10 +5531,10 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>77</v>
@@ -5544,39 +5555,39 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5587,7 +5598,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5599,16 +5610,16 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5658,28 +5669,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5687,10 +5698,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5713,13 +5724,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5770,7 +5781,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5782,27 +5793,27 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5816,7 +5827,7 @@
         <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -5825,13 +5836,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5882,7 +5893,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5894,13 +5905,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5911,14 +5922,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5937,16 +5948,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5996,7 +6007,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6008,13 +6019,13 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6025,10 +6036,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6039,7 +6050,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6051,17 +6062,17 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6110,25 +6121,25 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6139,10 +6150,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6153,7 +6164,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6165,13 +6176,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6222,13 +6233,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6240,7 +6251,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6251,14 +6262,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6277,16 +6288,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6336,7 +6347,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6348,13 +6359,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6365,14 +6376,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6385,25 +6396,25 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6452,7 +6463,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6464,13 +6475,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6481,10 +6492,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6495,7 +6506,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6507,17 +6518,17 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6566,25 +6577,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6595,10 +6606,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6609,7 +6620,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6621,19 +6632,19 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6682,25 +6693,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6711,10 +6722,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6737,13 +6748,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6794,7 +6805,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6806,13 +6817,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6823,14 +6834,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6849,17 +6860,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6908,7 +6919,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6920,13 +6931,13 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6937,10 +6948,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6951,7 +6962,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6963,13 +6974,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7020,13 +7031,13 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
@@ -7038,7 +7049,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7049,14 +7060,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7075,16 +7086,16 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7134,7 +7145,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7146,13 +7157,13 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7163,14 +7174,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7183,25 +7194,25 @@
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7250,7 +7261,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7262,13 +7273,13 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7279,21 +7290,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7305,19 +7316,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7342,10 +7353,10 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>77</v>
@@ -7366,25 +7377,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7395,10 +7406,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7406,10 +7417,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7421,13 +7432,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7478,25 +7489,25 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7507,10 +7518,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7533,17 +7544,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7592,7 +7603,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7604,13 +7615,13 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7621,10 +7632,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7635,7 +7646,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7647,13 +7658,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7704,13 +7715,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7722,7 +7733,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7733,14 +7744,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7759,16 +7770,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7818,7 +7829,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7830,13 +7841,13 @@
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7847,14 +7858,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7867,25 +7878,25 @@
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7934,7 +7945,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7946,13 +7957,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7963,21 +7974,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7989,17 +8000,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8024,10 +8035,10 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>77</v>
@@ -8048,25 +8059,25 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8077,10 +8088,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8088,10 +8099,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8103,17 +8114,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8162,25 +8173,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="423">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -274,9 +274,6 @@
     <t>ControlAct[moodCode=INT]</t>
   </si>
   <si>
-    <t>workflow.order</t>
-  </si>
-  <si>
     <t>Task.id</t>
   </si>
   <si>
@@ -360,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -418,10 +415,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -462,7 +455,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -601,7 +594,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
   </si>
   <si>
     <t>Request.status, Event.status</t>
@@ -672,7 +665,7 @@
     <t>Distinguishes whether the task is a proposal, plan or full order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/task-intent|4.0.1</t>
   </si>
   <si>
     <t>Request.intent</t>
@@ -699,10 +692,10 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>The priority of a task (may affect service level applied to the task).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.3.0</t>
+    <t>The task's priority.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
   </si>
   <si>
     <t>Request.priority</t>
@@ -1128,10 +1121,6 @@
   </si>
   <si>
     <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
@@ -1928,7 +1917,7 @@
         <v>84</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>77</v>
@@ -1936,10 +1925,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1950,28 +1939,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2021,13 +2010,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2050,10 +2039,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2064,25 +2053,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2133,19 +2122,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2162,10 +2151,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2176,28 +2165,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2247,19 +2236,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2276,10 +2265,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2290,7 +2279,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2302,16 +2291,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2337,43 +2326,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2390,21 +2379,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2416,16 +2405,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2475,25 +2464,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2504,14 +2493,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2530,16 +2519,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2589,7 +2578,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2601,13 +2590,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2618,14 +2607,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2644,16 +2633,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2703,7 +2692,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2715,13 +2704,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2732,14 +2721,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2752,25 +2741,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2819,7 +2808,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2831,13 +2820,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2848,10 +2837,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2874,13 +2863,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2931,7 +2920,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2943,16 +2932,16 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>77</v>
@@ -2960,10 +2949,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2974,29 +2963,29 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3045,25 +3034,25 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3074,10 +3063,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3088,29 +3077,29 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3159,25 +3148,25 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3188,10 +3177,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3211,16 +3200,16 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3271,7 +3260,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3283,13 +3272,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3300,10 +3289,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3314,29 +3303,29 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3385,25 +3374,25 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3414,10 +3403,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3437,22 +3426,22 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3501,7 +3490,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3513,13 +3502,13 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3530,10 +3519,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3541,32 +3530,32 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G17" t="s" s="2">
+      <c r="J17" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3591,52 +3580,52 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Z17" t="s" s="2">
+      <c r="AL17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3644,10 +3633,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3658,28 +3647,28 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3705,49 +3694,49 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3758,10 +3747,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3772,29 +3761,29 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K19" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3819,10 +3808,10 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>77</v>
@@ -3843,25 +3832,25 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3872,10 +3861,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3883,31 +3872,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3933,52 +3922,52 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AL20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AA20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3986,10 +3975,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4000,7 +3989,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
@@ -4012,89 +4001,89 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y21" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="P21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q21" t="s" s="2">
+      <c r="Z21" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="R21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="Y21" t="s" s="2">
+      <c r="AA21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK21" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="Z21" t="s" s="2">
+      <c r="AL21" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AA21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4102,10 +4091,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4116,28 +4105,28 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4163,52 +4152,52 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4216,10 +4205,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4230,25 +4219,25 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4299,25 +4288,25 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4328,10 +4317,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4342,31 +4331,31 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4415,28 +4404,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4444,43 +4433,43 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4529,28 +4518,28 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4558,10 +4547,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4572,29 +4561,29 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4643,28 +4632,28 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4672,10 +4661,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4683,28 +4672,28 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4755,28 +4744,28 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4784,21 +4773,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4810,17 +4799,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4869,28 +4858,28 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4898,43 +4887,43 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4983,25 +4972,25 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5012,10 +5001,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5026,29 +5015,29 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5097,28 +5086,28 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5126,10 +5115,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5152,17 +5141,17 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5187,13 +5176,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5211,7 +5200,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5223,16 +5212,16 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5240,45 +5229,45 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5327,28 +5316,28 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5356,10 +5345,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5370,29 +5359,29 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K33" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5441,28 +5430,28 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5470,10 +5459,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5484,7 +5473,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5496,16 +5485,16 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5531,63 +5520,63 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5598,7 +5587,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5610,16 +5599,16 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5669,28 +5658,28 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5698,10 +5687,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5724,13 +5713,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5781,7 +5770,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5793,27 +5782,27 @@
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5827,7 +5816,7 @@
         <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -5836,13 +5825,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5893,7 +5882,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5905,13 +5894,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5922,14 +5911,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5948,16 +5937,16 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6007,7 +5996,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6019,13 +6008,13 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6036,10 +6025,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6050,7 +6039,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6062,17 +6051,17 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6121,25 +6110,25 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6150,10 +6139,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6164,7 +6153,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6176,13 +6165,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6233,13 +6222,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6251,7 +6240,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6262,14 +6251,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6288,16 +6277,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6347,7 +6336,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6359,13 +6348,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6376,14 +6365,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6396,25 +6385,25 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6463,7 +6452,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6475,13 +6464,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6492,10 +6481,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6506,7 +6495,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6518,17 +6507,17 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6577,25 +6566,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6606,10 +6595,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6620,7 +6609,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6632,19 +6621,19 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6693,25 +6682,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6722,10 +6711,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6748,13 +6737,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6805,7 +6794,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6817,13 +6806,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6834,14 +6823,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6860,17 +6849,17 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6919,7 +6908,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6931,13 +6920,13 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6948,10 +6937,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6962,7 +6951,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6974,13 +6963,13 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7031,13 +7020,13 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
@@ -7049,7 +7038,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7060,14 +7049,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7086,16 +7075,16 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7145,7 +7134,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7157,13 +7146,13 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7174,14 +7163,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7194,25 +7183,25 @@
         <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7261,7 +7250,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7273,13 +7262,13 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7290,21 +7279,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7316,19 +7305,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7353,10 +7342,10 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>77</v>
@@ -7377,25 +7366,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7406,10 +7395,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7417,10 +7406,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
@@ -7432,13 +7421,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7489,25 +7478,25 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7518,10 +7507,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7544,17 +7533,17 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7603,7 +7592,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7615,13 +7604,13 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7632,10 +7621,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7646,7 +7635,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7658,13 +7647,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7715,13 +7704,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -7733,7 +7722,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7744,14 +7733,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7770,16 +7759,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7829,7 +7818,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7841,13 +7830,13 @@
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7858,14 +7847,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7878,25 +7867,25 @@
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7945,7 +7934,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7957,13 +7946,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7974,21 +7963,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8000,17 +7989,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8035,10 +8024,10 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>77</v>
@@ -8059,25 +8048,25 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8088,10 +8077,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8099,10 +8088,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8114,17 +8103,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8173,25 +8162,25 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
+++ b/branches/Richard/StructureDefinition-sample-dispatched-to-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
